--- a/ficha/ficha-projeto-m.xlsx
+++ b/ficha/ficha-projeto-m.xlsx
@@ -12887,7 +12887,7 @@
       </c>
       <c r="H4" s="72" t="inlineStr">
         <is>
-          <t>Lento</t>
+          <t>Lento (condição)</t>
         </is>
       </c>
       <c r="I4" s="72" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="G5" s="72" t="inlineStr">
         <is>
-          <t>Lento</t>
+          <t>Lento (restrição)</t>
         </is>
       </c>
       <c r="H5" s="72" t="inlineStr">

--- a/ficha/ficha-projeto-m.xlsx
+++ b/ficha/ficha-projeto-m.xlsx
@@ -12887,7 +12887,7 @@
       </c>
       <c r="H4" s="72" t="inlineStr">
         <is>
-          <t>Lento (condição)</t>
+          <t>Lento</t>
         </is>
       </c>
       <c r="I4" s="72" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="G5" s="72" t="inlineStr">
         <is>
-          <t>Lento (restrição)</t>
+          <t>Lento</t>
         </is>
       </c>
       <c r="H5" s="72" t="inlineStr">

--- a/ficha/ficha-projeto-m.xlsx
+++ b/ficha/ficha-projeto-m.xlsx
@@ -449,6 +449,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -456,9 +459,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -761,7 +761,7 @@
     <from>
       <col>42</col>
       <colOff>0</colOff>
-      <row>138</row>
+      <row>146</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="857250" cy="857250"/>
@@ -2908,7 +2908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AT140"/>
+  <dimension ref="A1:AT148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6090,13 +6090,13 @@
           <t>Condução</t>
         </is>
       </c>
-      <c r="M76" s="44" t="inlineStr">
-        <is>
-          <t>Des</t>
+      <c r="K76" s="39" t="inlineStr">
+        <is>
+          <t>Destreza</t>
         </is>
       </c>
       <c r="O76" s="45">
-        <f>$L$17+IF($E$76=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($D$76=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
+        <f>IF($K$76="Força",$D$17,IF($K$76="Destreza",$L$17,IF($K$76="Constituição",$T$17,IF($K$76="Inteligência",$AB$17,IF($K$76="Essência",$AJ$17,0)))))+IF($E$76=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($D$76=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
         <v/>
       </c>
       <c r="Q76" s="23" t="n"/>
@@ -6107,13 +6107,13 @@
           <t>Entalhador</t>
         </is>
       </c>
-      <c r="AA76" s="44" t="inlineStr">
-        <is>
-          <t>Des</t>
+      <c r="Y76" s="39" t="inlineStr">
+        <is>
+          <t>Destreza</t>
         </is>
       </c>
       <c r="AC76" s="45">
-        <f>$L$17+IF($S$76=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($R$76=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
+        <f>IF($Y$76="Força",$D$17,IF($Y$76="Destreza",$L$17,IF($Y$76="Constituição",$T$17,IF($Y$76="Inteligência",$AB$17,IF($Y$76="Essência",$AJ$17,0)))))+IF($S$76=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($R$76=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
         <v/>
       </c>
       <c r="AE76" s="23" t="n"/>
@@ -6148,16 +6148,16 @@
       <c r="H77" s="48" t="n"/>
       <c r="I77" s="48" t="n"/>
       <c r="J77" s="48" t="n"/>
-      <c r="K77" s="48" t="n"/>
+      <c r="K77" s="52" t="inlineStr">
+        <is>
+          <t>Destreza</t>
+        </is>
+      </c>
       <c r="L77" s="48" t="n"/>
-      <c r="M77" s="49" t="inlineStr">
-        <is>
-          <t>Des</t>
-        </is>
-      </c>
+      <c r="M77" s="48" t="n"/>
       <c r="N77" s="48" t="n"/>
       <c r="O77" s="50">
-        <f>$L$17+IF($E$77=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($D$77=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
+        <f>IF($K$77="Força",$D$17,IF($K$77="Destreza",$L$17,IF($K$77="Constituição",$T$17,IF($K$77="Inteligência",$AB$17,IF($K$77="Essência",$AJ$17,0)))))+IF($E$77=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($D$77=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
         <v/>
       </c>
       <c r="P77" s="48" t="n"/>
@@ -6173,16 +6173,16 @@
       <c r="V77" s="48" t="n"/>
       <c r="W77" s="48" t="n"/>
       <c r="X77" s="48" t="n"/>
-      <c r="Y77" s="48" t="n"/>
+      <c r="Y77" s="52" t="inlineStr">
+        <is>
+          <t>Destreza</t>
+        </is>
+      </c>
       <c r="Z77" s="48" t="n"/>
-      <c r="AA77" s="49" t="inlineStr">
-        <is>
-          <t>Des</t>
-        </is>
-      </c>
+      <c r="AA77" s="48" t="n"/>
       <c r="AB77" s="48" t="n"/>
       <c r="AC77" s="50">
-        <f>$L$17+IF($S$77=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($R$77=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
+        <f>IF($Y$77="Força",$D$17,IF($Y$77="Destreza",$L$17,IF($Y$77="Constituição",$T$17,IF($Y$77="Inteligência",$AB$17,IF($Y$77="Essência",$AJ$17,0)))))+IF($S$77=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($R$77=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
         <v/>
       </c>
       <c r="AD77" s="48" t="n"/>
@@ -6218,16 +6218,16 @@
       <c r="H78" s="48" t="n"/>
       <c r="I78" s="48" t="n"/>
       <c r="J78" s="48" t="n"/>
-      <c r="K78" s="48" t="n"/>
+      <c r="K78" s="52" t="inlineStr">
+        <is>
+          <t>Inteligência</t>
+        </is>
+      </c>
       <c r="L78" s="48" t="n"/>
-      <c r="M78" s="49" t="inlineStr">
-        <is>
-          <t>Int</t>
-        </is>
-      </c>
+      <c r="M78" s="48" t="n"/>
       <c r="N78" s="48" t="n"/>
       <c r="O78" s="50">
-        <f>$AB$17+IF($E$78=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($D$78=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
+        <f>IF($K$78="Força",$D$17,IF($K$78="Destreza",$L$17,IF($K$78="Constituição",$T$17,IF($K$78="Inteligência",$AB$17,IF($K$78="Essência",$AJ$17,0)))))+IF($E$78=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($D$78=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
         <v/>
       </c>
       <c r="P78" s="48" t="n"/>
@@ -6243,16 +6243,16 @@
       <c r="V78" s="48" t="n"/>
       <c r="W78" s="48" t="n"/>
       <c r="X78" s="48" t="n"/>
-      <c r="Y78" s="48" t="n"/>
+      <c r="Y78" s="52" t="inlineStr">
+        <is>
+          <t>Inteligência</t>
+        </is>
+      </c>
       <c r="Z78" s="48" t="n"/>
-      <c r="AA78" s="49" t="inlineStr">
-        <is>
-          <t>Int</t>
-        </is>
-      </c>
+      <c r="AA78" s="48" t="n"/>
       <c r="AB78" s="48" t="n"/>
       <c r="AC78" s="50">
-        <f>$AB$17+IF($S$78=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($R$78=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
+        <f>IF($Y$78="Força",$D$17,IF($Y$78="Destreza",$L$17,IF($Y$78="Constituição",$T$17,IF($Y$78="Inteligência",$AB$17,IF($Y$78="Essência",$AJ$17,0)))))+IF($S$78=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($R$78=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
         <v/>
       </c>
       <c r="AD78" s="48" t="n"/>
@@ -6288,16 +6288,16 @@
       <c r="H79" s="48" t="n"/>
       <c r="I79" s="48" t="n"/>
       <c r="J79" s="48" t="n"/>
-      <c r="K79" s="48" t="n"/>
+      <c r="K79" s="52" t="inlineStr">
+        <is>
+          <t>Força</t>
+        </is>
+      </c>
       <c r="L79" s="48" t="n"/>
-      <c r="M79" s="49" t="inlineStr">
-        <is>
-          <t>For</t>
-        </is>
-      </c>
+      <c r="M79" s="48" t="n"/>
       <c r="N79" s="48" t="n"/>
       <c r="O79" s="50">
-        <f>$D$17+IF($E$79=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($D$79=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
+        <f>IF($K$79="Força",$D$17,IF($K$79="Destreza",$L$17,IF($K$79="Constituição",$T$17,IF($K$79="Inteligência",$AB$17,IF($K$79="Essência",$AJ$17,0)))))+IF($E$79=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($D$79=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
         <v/>
       </c>
       <c r="P79" s="48" t="n"/>
@@ -6313,16 +6313,16 @@
       <c r="V79" s="48" t="n"/>
       <c r="W79" s="48" t="n"/>
       <c r="X79" s="48" t="n"/>
-      <c r="Y79" s="48" t="n"/>
+      <c r="Y79" s="52" t="inlineStr">
+        <is>
+          <t>Essência</t>
+        </is>
+      </c>
       <c r="Z79" s="48" t="n"/>
-      <c r="AA79" s="49" t="inlineStr">
-        <is>
-          <t>Ess</t>
-        </is>
-      </c>
+      <c r="AA79" s="48" t="n"/>
       <c r="AB79" s="48" t="n"/>
       <c r="AC79" s="50">
-        <f>$AJ$17+IF($S$79=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($R$79=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
+        <f>IF($Y$79="Força",$D$17,IF($Y$79="Destreza",$L$17,IF($Y$79="Constituição",$T$17,IF($Y$79="Inteligência",$AB$17,IF($Y$79="Essência",$AJ$17,0)))))+IF($S$79=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($R$79=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
         <v/>
       </c>
       <c r="AD79" s="48" t="n"/>
@@ -6358,16 +6358,16 @@
       <c r="H80" s="48" t="n"/>
       <c r="I80" s="48" t="n"/>
       <c r="J80" s="48" t="n"/>
-      <c r="K80" s="48" t="n"/>
+      <c r="K80" s="52" t="inlineStr">
+        <is>
+          <t>Destreza</t>
+        </is>
+      </c>
       <c r="L80" s="48" t="n"/>
-      <c r="M80" s="49" t="inlineStr">
-        <is>
-          <t>Des</t>
-        </is>
-      </c>
+      <c r="M80" s="48" t="n"/>
       <c r="N80" s="48" t="n"/>
       <c r="O80" s="50">
-        <f>$L$17+IF($E$80=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($D$80=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
+        <f>IF($K$80="Força",$D$17,IF($K$80="Destreza",$L$17,IF($K$80="Constituição",$T$17,IF($K$80="Inteligência",$AB$17,IF($K$80="Essência",$AJ$17,0)))))+IF($E$80=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($D$80=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
         <v/>
       </c>
       <c r="P80" s="48" t="n"/>
@@ -6383,16 +6383,16 @@
       <c r="V80" s="48" t="n"/>
       <c r="W80" s="48" t="n"/>
       <c r="X80" s="48" t="n"/>
-      <c r="Y80" s="48" t="n"/>
+      <c r="Y80" s="52" t="inlineStr">
+        <is>
+          <t>Essência</t>
+        </is>
+      </c>
       <c r="Z80" s="48" t="n"/>
-      <c r="AA80" s="49" t="inlineStr">
-        <is>
-          <t>Ess</t>
-        </is>
-      </c>
+      <c r="AA80" s="48" t="n"/>
       <c r="AB80" s="48" t="n"/>
       <c r="AC80" s="50">
-        <f>$AJ$17+IF($S$80=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($R$80=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
+        <f>IF($Y$80="Força",$D$17,IF($Y$80="Destreza",$L$17,IF($Y$80="Constituição",$T$17,IF($Y$80="Inteligência",$AB$17,IF($Y$80="Essência",$AJ$17,0)))))+IF($S$80=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($R$80=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
         <v/>
       </c>
       <c r="AD80" s="48" t="n"/>
@@ -6428,16 +6428,16 @@
       <c r="H81" s="48" t="n"/>
       <c r="I81" s="48" t="n"/>
       <c r="J81" s="48" t="n"/>
-      <c r="K81" s="48" t="n"/>
+      <c r="K81" s="52" t="inlineStr">
+        <is>
+          <t>Inteligência</t>
+        </is>
+      </c>
       <c r="L81" s="48" t="n"/>
-      <c r="M81" s="49" t="inlineStr">
-        <is>
-          <t>Int</t>
-        </is>
-      </c>
+      <c r="M81" s="48" t="n"/>
       <c r="N81" s="48" t="n"/>
       <c r="O81" s="50">
-        <f>$AB$17+IF($E$81=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($D$81=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
+        <f>IF($K$81="Força",$D$17,IF($K$81="Destreza",$L$17,IF($K$81="Constituição",$T$17,IF($K$81="Inteligência",$AB$17,IF($K$81="Essência",$AJ$17,0)))))+IF($E$81=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))+INT((1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11))/2),IF($D$81=TRUE,(1+COUNTIF(DADOS!$X$5:$X$7,"&lt;="&amp;$AH$11)),0))</f>
         <v/>
       </c>
       <c r="P81" s="48" t="n"/>
@@ -6997,7 +6997,7 @@
       <c r="A93" s="7" t="n"/>
       <c r="B93" s="7" t="n"/>
       <c r="C93" s="23" t="n"/>
-      <c r="D93" s="52" t="inlineStr">
+      <c r="D93" s="53" t="inlineStr">
         <is>
           <t>CLASSE 0 · GRÁTIS, NÃO OCUPAM ESPAÇO</t>
         </is>
@@ -7034,7 +7034,7 @@
       <c r="B94" s="7" t="n"/>
       <c r="C94" s="23" t="n"/>
       <c r="D94" s="43" t="n"/>
-      <c r="N94" s="53" t="n"/>
+      <c r="N94" s="54" t="n"/>
       <c r="W94" s="39" t="n"/>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -7051,7 +7051,7 @@
       <c r="K95" s="48" t="n"/>
       <c r="L95" s="48" t="n"/>
       <c r="M95" s="48" t="n"/>
-      <c r="N95" s="54" t="n"/>
+      <c r="N95" s="55" t="n"/>
       <c r="O95" s="48" t="n"/>
       <c r="P95" s="48" t="n"/>
       <c r="Q95" s="48" t="n"/>
@@ -7060,7 +7060,7 @@
       <c r="T95" s="48" t="n"/>
       <c r="U95" s="48" t="n"/>
       <c r="V95" s="48" t="n"/>
-      <c r="W95" s="55" t="n"/>
+      <c r="W95" s="52" t="n"/>
       <c r="X95" s="48" t="n"/>
       <c r="Y95" s="48" t="n"/>
       <c r="Z95" s="48" t="n"/>
@@ -7099,7 +7099,7 @@
       <c r="K96" s="48" t="n"/>
       <c r="L96" s="48" t="n"/>
       <c r="M96" s="48" t="n"/>
-      <c r="N96" s="54" t="n"/>
+      <c r="N96" s="55" t="n"/>
       <c r="O96" s="48" t="n"/>
       <c r="P96" s="48" t="n"/>
       <c r="Q96" s="48" t="n"/>
@@ -7108,7 +7108,7 @@
       <c r="T96" s="48" t="n"/>
       <c r="U96" s="48" t="n"/>
       <c r="V96" s="48" t="n"/>
-      <c r="W96" s="55" t="n"/>
+      <c r="W96" s="52" t="n"/>
       <c r="X96" s="48" t="n"/>
       <c r="Y96" s="48" t="n"/>
       <c r="Z96" s="48" t="n"/>
@@ -7147,7 +7147,7 @@
       <c r="K97" s="48" t="n"/>
       <c r="L97" s="48" t="n"/>
       <c r="M97" s="48" t="n"/>
-      <c r="N97" s="54" t="n"/>
+      <c r="N97" s="55" t="n"/>
       <c r="O97" s="48" t="n"/>
       <c r="P97" s="48" t="n"/>
       <c r="Q97" s="48" t="n"/>
@@ -7156,7 +7156,7 @@
       <c r="T97" s="48" t="n"/>
       <c r="U97" s="48" t="n"/>
       <c r="V97" s="48" t="n"/>
-      <c r="W97" s="55" t="n"/>
+      <c r="W97" s="52" t="n"/>
       <c r="X97" s="48" t="n"/>
       <c r="Y97" s="48" t="n"/>
       <c r="Z97" s="48" t="n"/>
@@ -7195,7 +7195,7 @@
       <c r="K98" s="48" t="n"/>
       <c r="L98" s="48" t="n"/>
       <c r="M98" s="48" t="n"/>
-      <c r="N98" s="54" t="n"/>
+      <c r="N98" s="55" t="n"/>
       <c r="O98" s="48" t="n"/>
       <c r="P98" s="48" t="n"/>
       <c r="Q98" s="48" t="n"/>
@@ -7204,7 +7204,7 @@
       <c r="T98" s="48" t="n"/>
       <c r="U98" s="48" t="n"/>
       <c r="V98" s="48" t="n"/>
-      <c r="W98" s="55" t="n"/>
+      <c r="W98" s="52" t="n"/>
       <c r="X98" s="48" t="n"/>
       <c r="Y98" s="48" t="n"/>
       <c r="Z98" s="48" t="n"/>
@@ -7351,7 +7351,7 @@
       <c r="C101" s="23" t="n"/>
       <c r="D101" s="56" t="n"/>
       <c r="G101" s="43" t="n"/>
-      <c r="Q101" s="53" t="n"/>
+      <c r="Q101" s="54" t="n"/>
       <c r="X101" s="57">
         <f>IF($D$101="","",$D$101*3)</f>
         <v/>
@@ -7375,7 +7375,7 @@
       <c r="N102" s="48" t="n"/>
       <c r="O102" s="48" t="n"/>
       <c r="P102" s="48" t="n"/>
-      <c r="Q102" s="54" t="n"/>
+      <c r="Q102" s="55" t="n"/>
       <c r="R102" s="48" t="n"/>
       <c r="S102" s="48" t="n"/>
       <c r="T102" s="48" t="n"/>
@@ -7389,7 +7389,7 @@
       <c r="Y102" s="48" t="n"/>
       <c r="Z102" s="48" t="n"/>
       <c r="AA102" s="48" t="n"/>
-      <c r="AB102" s="55" t="n"/>
+      <c r="AB102" s="52" t="n"/>
       <c r="AC102" s="48" t="n"/>
       <c r="AD102" s="48" t="n"/>
       <c r="AE102" s="48" t="n"/>
@@ -7426,7 +7426,7 @@
       <c r="N103" s="48" t="n"/>
       <c r="O103" s="48" t="n"/>
       <c r="P103" s="48" t="n"/>
-      <c r="Q103" s="54" t="n"/>
+      <c r="Q103" s="55" t="n"/>
       <c r="R103" s="48" t="n"/>
       <c r="S103" s="48" t="n"/>
       <c r="T103" s="48" t="n"/>
@@ -7440,7 +7440,7 @@
       <c r="Y103" s="48" t="n"/>
       <c r="Z103" s="48" t="n"/>
       <c r="AA103" s="48" t="n"/>
-      <c r="AB103" s="55" t="n"/>
+      <c r="AB103" s="52" t="n"/>
       <c r="AC103" s="48" t="n"/>
       <c r="AD103" s="48" t="n"/>
       <c r="AE103" s="48" t="n"/>
@@ -7477,7 +7477,7 @@
       <c r="N104" s="48" t="n"/>
       <c r="O104" s="48" t="n"/>
       <c r="P104" s="48" t="n"/>
-      <c r="Q104" s="54" t="n"/>
+      <c r="Q104" s="55" t="n"/>
       <c r="R104" s="48" t="n"/>
       <c r="S104" s="48" t="n"/>
       <c r="T104" s="48" t="n"/>
@@ -7491,7 +7491,7 @@
       <c r="Y104" s="48" t="n"/>
       <c r="Z104" s="48" t="n"/>
       <c r="AA104" s="48" t="n"/>
-      <c r="AB104" s="55" t="n"/>
+      <c r="AB104" s="52" t="n"/>
       <c r="AC104" s="48" t="n"/>
       <c r="AD104" s="48" t="n"/>
       <c r="AE104" s="48" t="n"/>
@@ -7528,7 +7528,7 @@
       <c r="N105" s="48" t="n"/>
       <c r="O105" s="48" t="n"/>
       <c r="P105" s="48" t="n"/>
-      <c r="Q105" s="54" t="n"/>
+      <c r="Q105" s="55" t="n"/>
       <c r="R105" s="48" t="n"/>
       <c r="S105" s="48" t="n"/>
       <c r="T105" s="48" t="n"/>
@@ -7542,7 +7542,7 @@
       <c r="Y105" s="48" t="n"/>
       <c r="Z105" s="48" t="n"/>
       <c r="AA105" s="48" t="n"/>
-      <c r="AB105" s="55" t="n"/>
+      <c r="AB105" s="52" t="n"/>
       <c r="AC105" s="48" t="n"/>
       <c r="AD105" s="48" t="n"/>
       <c r="AE105" s="48" t="n"/>
@@ -7579,7 +7579,7 @@
       <c r="N106" s="48" t="n"/>
       <c r="O106" s="48" t="n"/>
       <c r="P106" s="48" t="n"/>
-      <c r="Q106" s="54" t="n"/>
+      <c r="Q106" s="55" t="n"/>
       <c r="R106" s="48" t="n"/>
       <c r="S106" s="48" t="n"/>
       <c r="T106" s="48" t="n"/>
@@ -7593,7 +7593,7 @@
       <c r="Y106" s="48" t="n"/>
       <c r="Z106" s="48" t="n"/>
       <c r="AA106" s="48" t="n"/>
-      <c r="AB106" s="55" t="n"/>
+      <c r="AB106" s="52" t="n"/>
       <c r="AC106" s="48" t="n"/>
       <c r="AD106" s="48" t="n"/>
       <c r="AE106" s="48" t="n"/>
@@ -7630,7 +7630,7 @@
       <c r="N107" s="48" t="n"/>
       <c r="O107" s="48" t="n"/>
       <c r="P107" s="48" t="n"/>
-      <c r="Q107" s="54" t="n"/>
+      <c r="Q107" s="55" t="n"/>
       <c r="R107" s="48" t="n"/>
       <c r="S107" s="48" t="n"/>
       <c r="T107" s="48" t="n"/>
@@ -7644,7 +7644,7 @@
       <c r="Y107" s="48" t="n"/>
       <c r="Z107" s="48" t="n"/>
       <c r="AA107" s="48" t="n"/>
-      <c r="AB107" s="55" t="n"/>
+      <c r="AB107" s="52" t="n"/>
       <c r="AC107" s="48" t="n"/>
       <c r="AD107" s="48" t="n"/>
       <c r="AE107" s="48" t="n"/>
@@ -7681,7 +7681,7 @@
       <c r="N108" s="48" t="n"/>
       <c r="O108" s="48" t="n"/>
       <c r="P108" s="48" t="n"/>
-      <c r="Q108" s="54" t="n"/>
+      <c r="Q108" s="55" t="n"/>
       <c r="R108" s="48" t="n"/>
       <c r="S108" s="48" t="n"/>
       <c r="T108" s="48" t="n"/>
@@ -7695,7 +7695,7 @@
       <c r="Y108" s="48" t="n"/>
       <c r="Z108" s="48" t="n"/>
       <c r="AA108" s="48" t="n"/>
-      <c r="AB108" s="55" t="n"/>
+      <c r="AB108" s="52" t="n"/>
       <c r="AC108" s="48" t="n"/>
       <c r="AD108" s="48" t="n"/>
       <c r="AE108" s="48" t="n"/>
@@ -7732,7 +7732,7 @@
       <c r="N109" s="48" t="n"/>
       <c r="O109" s="48" t="n"/>
       <c r="P109" s="48" t="n"/>
-      <c r="Q109" s="54" t="n"/>
+      <c r="Q109" s="55" t="n"/>
       <c r="R109" s="48" t="n"/>
       <c r="S109" s="48" t="n"/>
       <c r="T109" s="48" t="n"/>
@@ -7746,7 +7746,7 @@
       <c r="Y109" s="48" t="n"/>
       <c r="Z109" s="48" t="n"/>
       <c r="AA109" s="48" t="n"/>
-      <c r="AB109" s="55" t="n"/>
+      <c r="AB109" s="52" t="n"/>
       <c r="AC109" s="48" t="n"/>
       <c r="AD109" s="48" t="n"/>
       <c r="AE109" s="48" t="n"/>
@@ -7783,7 +7783,7 @@
       <c r="N110" s="48" t="n"/>
       <c r="O110" s="48" t="n"/>
       <c r="P110" s="48" t="n"/>
-      <c r="Q110" s="54" t="n"/>
+      <c r="Q110" s="55" t="n"/>
       <c r="R110" s="48" t="n"/>
       <c r="S110" s="48" t="n"/>
       <c r="T110" s="48" t="n"/>
@@ -7797,7 +7797,7 @@
       <c r="Y110" s="48" t="n"/>
       <c r="Z110" s="48" t="n"/>
       <c r="AA110" s="48" t="n"/>
-      <c r="AB110" s="55" t="n"/>
+      <c r="AB110" s="52" t="n"/>
       <c r="AC110" s="48" t="n"/>
       <c r="AD110" s="48" t="n"/>
       <c r="AE110" s="48" t="n"/>
@@ -7834,7 +7834,7 @@
       <c r="N111" s="48" t="n"/>
       <c r="O111" s="48" t="n"/>
       <c r="P111" s="48" t="n"/>
-      <c r="Q111" s="54" t="n"/>
+      <c r="Q111" s="55" t="n"/>
       <c r="R111" s="48" t="n"/>
       <c r="S111" s="48" t="n"/>
       <c r="T111" s="48" t="n"/>
@@ -7848,7 +7848,7 @@
       <c r="Y111" s="48" t="n"/>
       <c r="Z111" s="48" t="n"/>
       <c r="AA111" s="48" t="n"/>
-      <c r="AB111" s="55" t="n"/>
+      <c r="AB111" s="52" t="n"/>
       <c r="AC111" s="48" t="n"/>
       <c r="AD111" s="48" t="n"/>
       <c r="AE111" s="48" t="n"/>
@@ -7885,7 +7885,7 @@
       <c r="N112" s="48" t="n"/>
       <c r="O112" s="48" t="n"/>
       <c r="P112" s="48" t="n"/>
-      <c r="Q112" s="54" t="n"/>
+      <c r="Q112" s="55" t="n"/>
       <c r="R112" s="48" t="n"/>
       <c r="S112" s="48" t="n"/>
       <c r="T112" s="48" t="n"/>
@@ -7899,7 +7899,7 @@
       <c r="Y112" s="48" t="n"/>
       <c r="Z112" s="48" t="n"/>
       <c r="AA112" s="48" t="n"/>
-      <c r="AB112" s="55" t="n"/>
+      <c r="AB112" s="52" t="n"/>
       <c r="AC112" s="48" t="n"/>
       <c r="AD112" s="48" t="n"/>
       <c r="AE112" s="48" t="n"/>
@@ -7936,7 +7936,7 @@
       <c r="N113" s="48" t="n"/>
       <c r="O113" s="48" t="n"/>
       <c r="P113" s="48" t="n"/>
-      <c r="Q113" s="54" t="n"/>
+      <c r="Q113" s="55" t="n"/>
       <c r="R113" s="48" t="n"/>
       <c r="S113" s="48" t="n"/>
       <c r="T113" s="48" t="n"/>
@@ -7950,7 +7950,7 @@
       <c r="Y113" s="48" t="n"/>
       <c r="Z113" s="48" t="n"/>
       <c r="AA113" s="48" t="n"/>
-      <c r="AB113" s="55" t="n"/>
+      <c r="AB113" s="52" t="n"/>
       <c r="AC113" s="48" t="n"/>
       <c r="AD113" s="48" t="n"/>
       <c r="AE113" s="48" t="n"/>
@@ -7987,7 +7987,7 @@
       <c r="N114" s="48" t="n"/>
       <c r="O114" s="48" t="n"/>
       <c r="P114" s="48" t="n"/>
-      <c r="Q114" s="54" t="n"/>
+      <c r="Q114" s="55" t="n"/>
       <c r="R114" s="48" t="n"/>
       <c r="S114" s="48" t="n"/>
       <c r="T114" s="48" t="n"/>
@@ -8001,7 +8001,7 @@
       <c r="Y114" s="48" t="n"/>
       <c r="Z114" s="48" t="n"/>
       <c r="AA114" s="48" t="n"/>
-      <c r="AB114" s="55" t="n"/>
+      <c r="AB114" s="52" t="n"/>
       <c r="AC114" s="48" t="n"/>
       <c r="AD114" s="48" t="n"/>
       <c r="AE114" s="48" t="n"/>
@@ -8038,7 +8038,7 @@
       <c r="N115" s="48" t="n"/>
       <c r="O115" s="48" t="n"/>
       <c r="P115" s="48" t="n"/>
-      <c r="Q115" s="54" t="n"/>
+      <c r="Q115" s="55" t="n"/>
       <c r="R115" s="48" t="n"/>
       <c r="S115" s="48" t="n"/>
       <c r="T115" s="48" t="n"/>
@@ -8052,7 +8052,7 @@
       <c r="Y115" s="48" t="n"/>
       <c r="Z115" s="48" t="n"/>
       <c r="AA115" s="48" t="n"/>
-      <c r="AB115" s="55" t="n"/>
+      <c r="AB115" s="52" t="n"/>
       <c r="AC115" s="48" t="n"/>
       <c r="AD115" s="48" t="n"/>
       <c r="AE115" s="48" t="n"/>
@@ -8089,7 +8089,7 @@
       <c r="N116" s="48" t="n"/>
       <c r="O116" s="48" t="n"/>
       <c r="P116" s="48" t="n"/>
-      <c r="Q116" s="54" t="n"/>
+      <c r="Q116" s="55" t="n"/>
       <c r="R116" s="48" t="n"/>
       <c r="S116" s="48" t="n"/>
       <c r="T116" s="48" t="n"/>
@@ -8103,7 +8103,7 @@
       <c r="Y116" s="48" t="n"/>
       <c r="Z116" s="48" t="n"/>
       <c r="AA116" s="48" t="n"/>
-      <c r="AB116" s="55" t="n"/>
+      <c r="AB116" s="52" t="n"/>
       <c r="AC116" s="48" t="n"/>
       <c r="AD116" s="48" t="n"/>
       <c r="AE116" s="48" t="n"/>
@@ -8140,7 +8140,7 @@
       <c r="N117" s="48" t="n"/>
       <c r="O117" s="48" t="n"/>
       <c r="P117" s="48" t="n"/>
-      <c r="Q117" s="54" t="n"/>
+      <c r="Q117" s="55" t="n"/>
       <c r="R117" s="48" t="n"/>
       <c r="S117" s="48" t="n"/>
       <c r="T117" s="48" t="n"/>
@@ -8154,7 +8154,7 @@
       <c r="Y117" s="48" t="n"/>
       <c r="Z117" s="48" t="n"/>
       <c r="AA117" s="48" t="n"/>
-      <c r="AB117" s="55" t="n"/>
+      <c r="AB117" s="52" t="n"/>
       <c r="AC117" s="48" t="n"/>
       <c r="AD117" s="48" t="n"/>
       <c r="AE117" s="48" t="n"/>
@@ -8191,7 +8191,7 @@
       <c r="N118" s="48" t="n"/>
       <c r="O118" s="48" t="n"/>
       <c r="P118" s="48" t="n"/>
-      <c r="Q118" s="54" t="n"/>
+      <c r="Q118" s="55" t="n"/>
       <c r="R118" s="48" t="n"/>
       <c r="S118" s="48" t="n"/>
       <c r="T118" s="48" t="n"/>
@@ -8205,7 +8205,7 @@
       <c r="Y118" s="48" t="n"/>
       <c r="Z118" s="48" t="n"/>
       <c r="AA118" s="48" t="n"/>
-      <c r="AB118" s="55" t="n"/>
+      <c r="AB118" s="52" t="n"/>
       <c r="AC118" s="48" t="n"/>
       <c r="AD118" s="48" t="n"/>
       <c r="AE118" s="48" t="n"/>
@@ -8242,7 +8242,7 @@
       <c r="N119" s="48" t="n"/>
       <c r="O119" s="48" t="n"/>
       <c r="P119" s="48" t="n"/>
-      <c r="Q119" s="54" t="n"/>
+      <c r="Q119" s="55" t="n"/>
       <c r="R119" s="48" t="n"/>
       <c r="S119" s="48" t="n"/>
       <c r="T119" s="48" t="n"/>
@@ -8256,7 +8256,7 @@
       <c r="Y119" s="48" t="n"/>
       <c r="Z119" s="48" t="n"/>
       <c r="AA119" s="48" t="n"/>
-      <c r="AB119" s="55" t="n"/>
+      <c r="AB119" s="52" t="n"/>
       <c r="AC119" s="48" t="n"/>
       <c r="AD119" s="48" t="n"/>
       <c r="AE119" s="48" t="n"/>
@@ -8293,7 +8293,7 @@
       <c r="N120" s="48" t="n"/>
       <c r="O120" s="48" t="n"/>
       <c r="P120" s="48" t="n"/>
-      <c r="Q120" s="54" t="n"/>
+      <c r="Q120" s="55" t="n"/>
       <c r="R120" s="48" t="n"/>
       <c r="S120" s="48" t="n"/>
       <c r="T120" s="48" t="n"/>
@@ -8307,7 +8307,7 @@
       <c r="Y120" s="48" t="n"/>
       <c r="Z120" s="48" t="n"/>
       <c r="AA120" s="48" t="n"/>
-      <c r="AB120" s="55" t="n"/>
+      <c r="AB120" s="52" t="n"/>
       <c r="AC120" s="48" t="n"/>
       <c r="AD120" s="48" t="n"/>
       <c r="AE120" s="48" t="n"/>
@@ -8344,7 +8344,7 @@
       <c r="N121" s="48" t="n"/>
       <c r="O121" s="48" t="n"/>
       <c r="P121" s="48" t="n"/>
-      <c r="Q121" s="54" t="n"/>
+      <c r="Q121" s="55" t="n"/>
       <c r="R121" s="48" t="n"/>
       <c r="S121" s="48" t="n"/>
       <c r="T121" s="48" t="n"/>
@@ -8358,7 +8358,7 @@
       <c r="Y121" s="48" t="n"/>
       <c r="Z121" s="48" t="n"/>
       <c r="AA121" s="48" t="n"/>
-      <c r="AB121" s="55" t="n"/>
+      <c r="AB121" s="52" t="n"/>
       <c r="AC121" s="48" t="n"/>
       <c r="AD121" s="48" t="n"/>
       <c r="AE121" s="48" t="n"/>
@@ -8395,7 +8395,7 @@
       <c r="N122" s="48" t="n"/>
       <c r="O122" s="48" t="n"/>
       <c r="P122" s="48" t="n"/>
-      <c r="Q122" s="54" t="n"/>
+      <c r="Q122" s="55" t="n"/>
       <c r="R122" s="48" t="n"/>
       <c r="S122" s="48" t="n"/>
       <c r="T122" s="48" t="n"/>
@@ -8409,7 +8409,7 @@
       <c r="Y122" s="48" t="n"/>
       <c r="Z122" s="48" t="n"/>
       <c r="AA122" s="48" t="n"/>
-      <c r="AB122" s="55" t="n"/>
+      <c r="AB122" s="52" t="n"/>
       <c r="AC122" s="48" t="n"/>
       <c r="AD122" s="48" t="n"/>
       <c r="AE122" s="48" t="n"/>
@@ -8446,7 +8446,7 @@
       <c r="N123" s="48" t="n"/>
       <c r="O123" s="48" t="n"/>
       <c r="P123" s="48" t="n"/>
-      <c r="Q123" s="54" t="n"/>
+      <c r="Q123" s="55" t="n"/>
       <c r="R123" s="48" t="n"/>
       <c r="S123" s="48" t="n"/>
       <c r="T123" s="48" t="n"/>
@@ -8460,7 +8460,7 @@
       <c r="Y123" s="48" t="n"/>
       <c r="Z123" s="48" t="n"/>
       <c r="AA123" s="48" t="n"/>
-      <c r="AB123" s="55" t="n"/>
+      <c r="AB123" s="52" t="n"/>
       <c r="AC123" s="48" t="n"/>
       <c r="AD123" s="48" t="n"/>
       <c r="AE123" s="48" t="n"/>
@@ -8497,7 +8497,7 @@
       <c r="N124" s="48" t="n"/>
       <c r="O124" s="48" t="n"/>
       <c r="P124" s="48" t="n"/>
-      <c r="Q124" s="54" t="n"/>
+      <c r="Q124" s="55" t="n"/>
       <c r="R124" s="48" t="n"/>
       <c r="S124" s="48" t="n"/>
       <c r="T124" s="48" t="n"/>
@@ -8511,7 +8511,7 @@
       <c r="Y124" s="48" t="n"/>
       <c r="Z124" s="48" t="n"/>
       <c r="AA124" s="48" t="n"/>
-      <c r="AB124" s="55" t="n"/>
+      <c r="AB124" s="52" t="n"/>
       <c r="AC124" s="48" t="n"/>
       <c r="AD124" s="48" t="n"/>
       <c r="AE124" s="48" t="n"/>
@@ -8583,19 +8583,44 @@
       <c r="A126" s="7" t="n"/>
       <c r="B126" s="7" t="n"/>
       <c r="C126" s="23" t="n"/>
-      <c r="D126" s="35">
-        <f>"Disponível: "&amp;($D$54-COUNTIF($D$101:$D$124,"&gt;0"))&amp;" · Conhecidos: "&amp;$D$54&amp;" · Classe 0: "&amp;($AK$54-COUNTIF($D$94:$D$98,"&lt;&gt;"))&amp;"/"&amp;$AK$54</f>
-        <v/>
-      </c>
+      <c r="D126" s="53" t="inlineStr">
+        <is>
+          <t>PASSIVAS PAGAS · custam espaço de feitiço, e a Classe é o preço. Máximo 5</t>
+        </is>
+      </c>
+      <c r="AE126" s="23" t="n"/>
+      <c r="AF126" s="23" t="n"/>
+      <c r="AG126" s="23" t="n"/>
+      <c r="AH126" s="23" t="n"/>
+      <c r="AI126" s="23" t="n"/>
+      <c r="AJ126" s="23" t="n"/>
+      <c r="AK126" s="23" t="n"/>
+      <c r="AL126" s="23" t="n"/>
+      <c r="AM126" s="23" t="n"/>
+      <c r="AN126" s="23" t="n"/>
+      <c r="AO126" s="23" t="n"/>
+      <c r="AP126" s="23" t="n"/>
+      <c r="AQ126" s="23" t="n"/>
+      <c r="AR126" s="23" t="n"/>
+      <c r="AS126" s="23" t="n"/>
+      <c r="AT126" s="23" t="n"/>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" s="7" t="n"/>
       <c r="B127" s="7" t="n"/>
       <c r="C127" s="23" t="n"/>
-      <c r="D127" s="23" t="n"/>
+      <c r="D127" s="27" t="inlineStr">
+        <is>
+          <t>CLASSE</t>
+        </is>
+      </c>
       <c r="E127" s="23" t="n"/>
       <c r="F127" s="23" t="n"/>
-      <c r="G127" s="23" t="n"/>
+      <c r="G127" s="27" t="inlineStr">
+        <is>
+          <t>NOME</t>
+        </is>
+      </c>
       <c r="H127" s="23" t="n"/>
       <c r="I127" s="23" t="n"/>
       <c r="J127" s="23" t="n"/>
@@ -8605,7 +8630,11 @@
       <c r="N127" s="23" t="n"/>
       <c r="O127" s="23" t="n"/>
       <c r="P127" s="23" t="n"/>
-      <c r="Q127" s="23" t="n"/>
+      <c r="Q127" s="27" t="inlineStr">
+        <is>
+          <t>O QUE ELA FAZ SOZINHA</t>
+        </is>
+      </c>
       <c r="R127" s="23" t="n"/>
       <c r="S127" s="23" t="n"/>
       <c r="T127" s="23" t="n"/>
@@ -8640,179 +8669,266 @@
       <c r="A128" s="7" t="n"/>
       <c r="B128" s="7" t="n"/>
       <c r="C128" s="23" t="n"/>
-      <c r="D128" s="25" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="G128" s="26" t="inlineStr">
-        <is>
-          <t>PASSIVA LIVRE · uma, de graça. Não rola dado, não muda número</t>
-        </is>
-      </c>
-      <c r="AI128" s="23" t="n"/>
-      <c r="AJ128" s="23" t="n"/>
-      <c r="AK128" s="23" t="n"/>
-      <c r="AL128" s="23" t="n"/>
-      <c r="AM128" s="23" t="n"/>
-      <c r="AN128" s="23" t="n"/>
-      <c r="AO128" s="23" t="n"/>
-      <c r="AP128" s="23" t="n"/>
-      <c r="AQ128" s="23" t="n"/>
-      <c r="AR128" s="23" t="n"/>
-      <c r="AS128" s="23" t="n"/>
-      <c r="AT128" s="23" t="n"/>
+      <c r="D128" s="56" t="n"/>
+      <c r="G128" s="43" t="n"/>
+      <c r="Q128" s="39" t="n"/>
     </row>
     <row r="129" ht="15" customHeight="1">
       <c r="A129" s="7" t="n"/>
       <c r="B129" s="7" t="n"/>
       <c r="C129" s="23" t="n"/>
-      <c r="G129" s="23" t="n"/>
-      <c r="H129" s="23" t="n"/>
-      <c r="I129" s="23" t="n"/>
-      <c r="J129" s="23" t="n"/>
-      <c r="K129" s="23" t="n"/>
-      <c r="L129" s="23" t="n"/>
-      <c r="M129" s="23" t="n"/>
-      <c r="N129" s="23" t="n"/>
-      <c r="O129" s="23" t="n"/>
-      <c r="P129" s="23" t="n"/>
-      <c r="Q129" s="23" t="n"/>
-      <c r="R129" s="23" t="n"/>
-      <c r="S129" s="23" t="n"/>
-      <c r="T129" s="23" t="n"/>
-      <c r="U129" s="23" t="n"/>
-      <c r="V129" s="23" t="n"/>
-      <c r="W129" s="23" t="n"/>
-      <c r="X129" s="23" t="n"/>
-      <c r="Y129" s="23" t="n"/>
-      <c r="Z129" s="23" t="n"/>
-      <c r="AA129" s="23" t="n"/>
-      <c r="AB129" s="23" t="n"/>
-      <c r="AC129" s="23" t="n"/>
-      <c r="AD129" s="23" t="n"/>
-      <c r="AE129" s="23" t="n"/>
-      <c r="AF129" s="23" t="n"/>
-      <c r="AG129" s="23" t="n"/>
-      <c r="AH129" s="23" t="n"/>
-      <c r="AI129" s="23" t="n"/>
-      <c r="AJ129" s="23" t="n"/>
-      <c r="AK129" s="23" t="n"/>
-      <c r="AL129" s="23" t="n"/>
-      <c r="AM129" s="23" t="n"/>
-      <c r="AN129" s="23" t="n"/>
-      <c r="AO129" s="23" t="n"/>
-      <c r="AP129" s="23" t="n"/>
-      <c r="AQ129" s="23" t="n"/>
-      <c r="AR129" s="23" t="n"/>
-      <c r="AS129" s="23" t="n"/>
-      <c r="AT129" s="23" t="n"/>
+      <c r="D129" s="58" t="n"/>
+      <c r="E129" s="48" t="n"/>
+      <c r="F129" s="48" t="n"/>
+      <c r="G129" s="47" t="n"/>
+      <c r="H129" s="48" t="n"/>
+      <c r="I129" s="48" t="n"/>
+      <c r="J129" s="48" t="n"/>
+      <c r="K129" s="48" t="n"/>
+      <c r="L129" s="48" t="n"/>
+      <c r="M129" s="48" t="n"/>
+      <c r="N129" s="48" t="n"/>
+      <c r="O129" s="48" t="n"/>
+      <c r="P129" s="48" t="n"/>
+      <c r="Q129" s="52" t="n"/>
+      <c r="R129" s="48" t="n"/>
+      <c r="S129" s="48" t="n"/>
+      <c r="T129" s="48" t="n"/>
+      <c r="U129" s="48" t="n"/>
+      <c r="V129" s="48" t="n"/>
+      <c r="W129" s="48" t="n"/>
+      <c r="X129" s="48" t="n"/>
+      <c r="Y129" s="48" t="n"/>
+      <c r="Z129" s="48" t="n"/>
+      <c r="AA129" s="48" t="n"/>
+      <c r="AB129" s="48" t="n"/>
+      <c r="AC129" s="48" t="n"/>
+      <c r="AD129" s="48" t="n"/>
+      <c r="AE129" s="48" t="n"/>
+      <c r="AF129" s="48" t="n"/>
+      <c r="AG129" s="48" t="n"/>
+      <c r="AH129" s="48" t="n"/>
+      <c r="AI129" s="48" t="n"/>
+      <c r="AJ129" s="48" t="n"/>
+      <c r="AK129" s="48" t="n"/>
+      <c r="AL129" s="48" t="n"/>
+      <c r="AM129" s="48" t="n"/>
+      <c r="AN129" s="48" t="n"/>
+      <c r="AO129" s="48" t="n"/>
+      <c r="AP129" s="48" t="n"/>
+      <c r="AQ129" s="48" t="n"/>
+      <c r="AR129" s="48" t="n"/>
+      <c r="AS129" s="48" t="n"/>
+      <c r="AT129" s="48" t="n"/>
     </row>
     <row r="130" ht="15" customHeight="1">
       <c r="A130" s="7" t="n"/>
       <c r="B130" s="7" t="n"/>
       <c r="C130" s="23" t="n"/>
-      <c r="D130" s="60" t="n"/>
+      <c r="D130" s="58" t="n"/>
+      <c r="E130" s="48" t="n"/>
+      <c r="F130" s="48" t="n"/>
+      <c r="G130" s="47" t="n"/>
+      <c r="H130" s="48" t="n"/>
+      <c r="I130" s="48" t="n"/>
+      <c r="J130" s="48" t="n"/>
+      <c r="K130" s="48" t="n"/>
+      <c r="L130" s="48" t="n"/>
+      <c r="M130" s="48" t="n"/>
+      <c r="N130" s="48" t="n"/>
+      <c r="O130" s="48" t="n"/>
+      <c r="P130" s="48" t="n"/>
+      <c r="Q130" s="52" t="n"/>
+      <c r="R130" s="48" t="n"/>
+      <c r="S130" s="48" t="n"/>
+      <c r="T130" s="48" t="n"/>
+      <c r="U130" s="48" t="n"/>
+      <c r="V130" s="48" t="n"/>
+      <c r="W130" s="48" t="n"/>
+      <c r="X130" s="48" t="n"/>
+      <c r="Y130" s="48" t="n"/>
+      <c r="Z130" s="48" t="n"/>
+      <c r="AA130" s="48" t="n"/>
+      <c r="AB130" s="48" t="n"/>
+      <c r="AC130" s="48" t="n"/>
+      <c r="AD130" s="48" t="n"/>
+      <c r="AE130" s="48" t="n"/>
+      <c r="AF130" s="48" t="n"/>
+      <c r="AG130" s="48" t="n"/>
+      <c r="AH130" s="48" t="n"/>
+      <c r="AI130" s="48" t="n"/>
+      <c r="AJ130" s="48" t="n"/>
+      <c r="AK130" s="48" t="n"/>
+      <c r="AL130" s="48" t="n"/>
+      <c r="AM130" s="48" t="n"/>
+      <c r="AN130" s="48" t="n"/>
+      <c r="AO130" s="48" t="n"/>
+      <c r="AP130" s="48" t="n"/>
+      <c r="AQ130" s="48" t="n"/>
+      <c r="AR130" s="48" t="n"/>
+      <c r="AS130" s="48" t="n"/>
+      <c r="AT130" s="48" t="n"/>
     </row>
     <row r="131" ht="15" customHeight="1">
       <c r="A131" s="7" t="n"/>
       <c r="B131" s="7" t="n"/>
       <c r="C131" s="23" t="n"/>
+      <c r="D131" s="58" t="n"/>
+      <c r="E131" s="48" t="n"/>
+      <c r="F131" s="48" t="n"/>
+      <c r="G131" s="47" t="n"/>
+      <c r="H131" s="48" t="n"/>
+      <c r="I131" s="48" t="n"/>
+      <c r="J131" s="48" t="n"/>
+      <c r="K131" s="48" t="n"/>
+      <c r="L131" s="48" t="n"/>
+      <c r="M131" s="48" t="n"/>
+      <c r="N131" s="48" t="n"/>
+      <c r="O131" s="48" t="n"/>
+      <c r="P131" s="48" t="n"/>
+      <c r="Q131" s="52" t="n"/>
+      <c r="R131" s="48" t="n"/>
+      <c r="S131" s="48" t="n"/>
+      <c r="T131" s="48" t="n"/>
+      <c r="U131" s="48" t="n"/>
+      <c r="V131" s="48" t="n"/>
+      <c r="W131" s="48" t="n"/>
+      <c r="X131" s="48" t="n"/>
+      <c r="Y131" s="48" t="n"/>
+      <c r="Z131" s="48" t="n"/>
+      <c r="AA131" s="48" t="n"/>
+      <c r="AB131" s="48" t="n"/>
+      <c r="AC131" s="48" t="n"/>
+      <c r="AD131" s="48" t="n"/>
+      <c r="AE131" s="48" t="n"/>
+      <c r="AF131" s="48" t="n"/>
+      <c r="AG131" s="48" t="n"/>
+      <c r="AH131" s="48" t="n"/>
+      <c r="AI131" s="48" t="n"/>
+      <c r="AJ131" s="48" t="n"/>
+      <c r="AK131" s="48" t="n"/>
+      <c r="AL131" s="48" t="n"/>
+      <c r="AM131" s="48" t="n"/>
+      <c r="AN131" s="48" t="n"/>
+      <c r="AO131" s="48" t="n"/>
+      <c r="AP131" s="48" t="n"/>
+      <c r="AQ131" s="48" t="n"/>
+      <c r="AR131" s="48" t="n"/>
+      <c r="AS131" s="48" t="n"/>
+      <c r="AT131" s="48" t="n"/>
     </row>
     <row r="132" ht="15" customHeight="1">
       <c r="A132" s="7" t="n"/>
       <c r="B132" s="7" t="n"/>
       <c r="C132" s="23" t="n"/>
+      <c r="D132" s="58" t="n"/>
+      <c r="E132" s="48" t="n"/>
+      <c r="F132" s="48" t="n"/>
+      <c r="G132" s="47" t="n"/>
+      <c r="H132" s="48" t="n"/>
+      <c r="I132" s="48" t="n"/>
+      <c r="J132" s="48" t="n"/>
+      <c r="K132" s="48" t="n"/>
+      <c r="L132" s="48" t="n"/>
+      <c r="M132" s="48" t="n"/>
+      <c r="N132" s="48" t="n"/>
+      <c r="O132" s="48" t="n"/>
+      <c r="P132" s="48" t="n"/>
+      <c r="Q132" s="52" t="n"/>
+      <c r="R132" s="48" t="n"/>
+      <c r="S132" s="48" t="n"/>
+      <c r="T132" s="48" t="n"/>
+      <c r="U132" s="48" t="n"/>
+      <c r="V132" s="48" t="n"/>
+      <c r="W132" s="48" t="n"/>
+      <c r="X132" s="48" t="n"/>
+      <c r="Y132" s="48" t="n"/>
+      <c r="Z132" s="48" t="n"/>
+      <c r="AA132" s="48" t="n"/>
+      <c r="AB132" s="48" t="n"/>
+      <c r="AC132" s="48" t="n"/>
+      <c r="AD132" s="48" t="n"/>
+      <c r="AE132" s="48" t="n"/>
+      <c r="AF132" s="48" t="n"/>
+      <c r="AG132" s="48" t="n"/>
+      <c r="AH132" s="48" t="n"/>
+      <c r="AI132" s="48" t="n"/>
+      <c r="AJ132" s="48" t="n"/>
+      <c r="AK132" s="48" t="n"/>
+      <c r="AL132" s="48" t="n"/>
+      <c r="AM132" s="48" t="n"/>
+      <c r="AN132" s="48" t="n"/>
+      <c r="AO132" s="48" t="n"/>
+      <c r="AP132" s="48" t="n"/>
+      <c r="AQ132" s="48" t="n"/>
+      <c r="AR132" s="48" t="n"/>
+      <c r="AS132" s="48" t="n"/>
+      <c r="AT132" s="48" t="n"/>
     </row>
     <row r="133" ht="15" customHeight="1">
       <c r="A133" s="7" t="n"/>
       <c r="B133" s="7" t="n"/>
       <c r="C133" s="23" t="n"/>
-      <c r="D133" s="23" t="n"/>
-      <c r="E133" s="23" t="n"/>
-      <c r="F133" s="23" t="n"/>
-      <c r="G133" s="23" t="n"/>
-      <c r="H133" s="23" t="n"/>
-      <c r="I133" s="23" t="n"/>
-      <c r="J133" s="23" t="n"/>
-      <c r="K133" s="23" t="n"/>
-      <c r="L133" s="23" t="n"/>
-      <c r="M133" s="23" t="n"/>
-      <c r="N133" s="23" t="n"/>
-      <c r="O133" s="23" t="n"/>
-      <c r="P133" s="23" t="n"/>
-      <c r="Q133" s="23" t="n"/>
-      <c r="R133" s="23" t="n"/>
-      <c r="S133" s="23" t="n"/>
-      <c r="T133" s="23" t="n"/>
-      <c r="U133" s="23" t="n"/>
-      <c r="V133" s="23" t="n"/>
-      <c r="W133" s="23" t="n"/>
-      <c r="X133" s="23" t="n"/>
-      <c r="Y133" s="23" t="n"/>
-      <c r="Z133" s="23" t="n"/>
-      <c r="AA133" s="23" t="n"/>
-      <c r="AB133" s="23" t="n"/>
-      <c r="AC133" s="23" t="n"/>
-      <c r="AD133" s="23" t="n"/>
-      <c r="AE133" s="23" t="n"/>
-      <c r="AF133" s="23" t="n"/>
-      <c r="AG133" s="23" t="n"/>
-      <c r="AH133" s="23" t="n"/>
-      <c r="AI133" s="23" t="n"/>
-      <c r="AJ133" s="23" t="n"/>
-      <c r="AK133" s="23" t="n"/>
-      <c r="AL133" s="23" t="n"/>
-      <c r="AM133" s="23" t="n"/>
-      <c r="AN133" s="23" t="n"/>
-      <c r="AO133" s="23" t="n"/>
-      <c r="AP133" s="23" t="n"/>
-      <c r="AQ133" s="23" t="n"/>
-      <c r="AR133" s="23" t="n"/>
-      <c r="AS133" s="23" t="n"/>
-      <c r="AT133" s="23" t="n"/>
+      <c r="D133" s="51" t="n"/>
+      <c r="E133" s="51" t="n"/>
+      <c r="F133" s="51" t="n"/>
+      <c r="G133" s="51" t="n"/>
+      <c r="H133" s="51" t="n"/>
+      <c r="I133" s="51" t="n"/>
+      <c r="J133" s="51" t="n"/>
+      <c r="K133" s="51" t="n"/>
+      <c r="L133" s="51" t="n"/>
+      <c r="M133" s="51" t="n"/>
+      <c r="N133" s="51" t="n"/>
+      <c r="O133" s="51" t="n"/>
+      <c r="P133" s="51" t="n"/>
+      <c r="Q133" s="51" t="n"/>
+      <c r="R133" s="51" t="n"/>
+      <c r="S133" s="51" t="n"/>
+      <c r="T133" s="51" t="n"/>
+      <c r="U133" s="51" t="n"/>
+      <c r="V133" s="51" t="n"/>
+      <c r="W133" s="51" t="n"/>
+      <c r="X133" s="51" t="n"/>
+      <c r="Y133" s="51" t="n"/>
+      <c r="Z133" s="51" t="n"/>
+      <c r="AA133" s="51" t="n"/>
+      <c r="AB133" s="51" t="n"/>
+      <c r="AC133" s="51" t="n"/>
+      <c r="AD133" s="51" t="n"/>
+      <c r="AE133" s="51" t="n"/>
+      <c r="AF133" s="51" t="n"/>
+      <c r="AG133" s="51" t="n"/>
+      <c r="AH133" s="51" t="n"/>
+      <c r="AI133" s="51" t="n"/>
+      <c r="AJ133" s="51" t="n"/>
+      <c r="AK133" s="51" t="n"/>
+      <c r="AL133" s="51" t="n"/>
+      <c r="AM133" s="51" t="n"/>
+      <c r="AN133" s="51" t="n"/>
+      <c r="AO133" s="51" t="n"/>
+      <c r="AP133" s="51" t="n"/>
+      <c r="AQ133" s="51" t="n"/>
+      <c r="AR133" s="51" t="n"/>
+      <c r="AS133" s="51" t="n"/>
+      <c r="AT133" s="51" t="n"/>
     </row>
     <row r="134" ht="15" customHeight="1">
       <c r="A134" s="7" t="n"/>
       <c r="B134" s="7" t="n"/>
       <c r="C134" s="23" t="n"/>
-      <c r="D134" s="25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G134" s="26" t="inlineStr">
-        <is>
-          <t>ANOTAÇÕES</t>
-        </is>
-      </c>
-      <c r="Y134" s="23" t="n"/>
-      <c r="Z134" s="23" t="n"/>
-      <c r="AA134" s="23" t="n"/>
-      <c r="AB134" s="23" t="n"/>
-      <c r="AC134" s="23" t="n"/>
-      <c r="AD134" s="23" t="n"/>
-      <c r="AE134" s="23" t="n"/>
-      <c r="AF134" s="23" t="n"/>
-      <c r="AG134" s="23" t="n"/>
-      <c r="AH134" s="23" t="n"/>
-      <c r="AI134" s="23" t="n"/>
-      <c r="AJ134" s="23" t="n"/>
-      <c r="AK134" s="23" t="n"/>
-      <c r="AL134" s="23" t="n"/>
-      <c r="AM134" s="23" t="n"/>
-      <c r="AN134" s="23" t="n"/>
-      <c r="AO134" s="23" t="n"/>
-      <c r="AP134" s="23" t="n"/>
-      <c r="AQ134" s="23" t="n"/>
-      <c r="AR134" s="23" t="n"/>
-      <c r="AS134" s="23" t="n"/>
-      <c r="AT134" s="23" t="n"/>
+      <c r="D134" s="35">
+        <f>"Disponível: "&amp;($D$54-COUNTIF($D$101:$D$124,"&gt;0")-SUM($D$128:$D$132))&amp;" · Conhecidos: "&amp;$D$54&amp;" · Passivas: "&amp;COUNTIF($D$128:$D$132,"&gt;0")&amp;"/5"&amp;" · Classe 0: "&amp;($AK$54-COUNTIF($D$94:$D$98,"&lt;&gt;"))&amp;"/"&amp;$AK$54</f>
+        <v/>
+      </c>
     </row>
     <row r="135" ht="15" customHeight="1">
       <c r="A135" s="7" t="n"/>
       <c r="B135" s="7" t="n"/>
       <c r="C135" s="23" t="n"/>
+      <c r="D135" s="23" t="n"/>
+      <c r="E135" s="23" t="n"/>
+      <c r="F135" s="23" t="n"/>
       <c r="G135" s="23" t="n"/>
       <c r="H135" s="23" t="n"/>
       <c r="I135" s="23" t="n"/>
@@ -8858,41 +8974,257 @@
       <c r="A136" s="7" t="n"/>
       <c r="B136" s="7" t="n"/>
       <c r="C136" s="23" t="n"/>
-      <c r="D136" s="35" t="n"/>
+      <c r="D136" s="25" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="G136" s="26" t="inlineStr">
+        <is>
+          <t>PASSIVA LIVRE · de graça, fora do teto. Não rola dado, não muda número</t>
+        </is>
+      </c>
+      <c r="AM136" s="23" t="n"/>
+      <c r="AN136" s="23" t="n"/>
+      <c r="AO136" s="23" t="n"/>
+      <c r="AP136" s="23" t="n"/>
+      <c r="AQ136" s="23" t="n"/>
+      <c r="AR136" s="23" t="n"/>
+      <c r="AS136" s="23" t="n"/>
+      <c r="AT136" s="23" t="n"/>
     </row>
     <row r="137" ht="15" customHeight="1">
       <c r="A137" s="7" t="n"/>
       <c r="B137" s="7" t="n"/>
       <c r="C137" s="23" t="n"/>
+      <c r="G137" s="23" t="n"/>
+      <c r="H137" s="23" t="n"/>
+      <c r="I137" s="23" t="n"/>
+      <c r="J137" s="23" t="n"/>
+      <c r="K137" s="23" t="n"/>
+      <c r="L137" s="23" t="n"/>
+      <c r="M137" s="23" t="n"/>
+      <c r="N137" s="23" t="n"/>
+      <c r="O137" s="23" t="n"/>
+      <c r="P137" s="23" t="n"/>
+      <c r="Q137" s="23" t="n"/>
+      <c r="R137" s="23" t="n"/>
+      <c r="S137" s="23" t="n"/>
+      <c r="T137" s="23" t="n"/>
+      <c r="U137" s="23" t="n"/>
+      <c r="V137" s="23" t="n"/>
+      <c r="W137" s="23" t="n"/>
+      <c r="X137" s="23" t="n"/>
+      <c r="Y137" s="23" t="n"/>
+      <c r="Z137" s="23" t="n"/>
+      <c r="AA137" s="23" t="n"/>
+      <c r="AB137" s="23" t="n"/>
+      <c r="AC137" s="23" t="n"/>
+      <c r="AD137" s="23" t="n"/>
+      <c r="AE137" s="23" t="n"/>
+      <c r="AF137" s="23" t="n"/>
+      <c r="AG137" s="23" t="n"/>
+      <c r="AH137" s="23" t="n"/>
+      <c r="AI137" s="23" t="n"/>
+      <c r="AJ137" s="23" t="n"/>
+      <c r="AK137" s="23" t="n"/>
+      <c r="AL137" s="23" t="n"/>
+      <c r="AM137" s="23" t="n"/>
+      <c r="AN137" s="23" t="n"/>
+      <c r="AO137" s="23" t="n"/>
+      <c r="AP137" s="23" t="n"/>
+      <c r="AQ137" s="23" t="n"/>
+      <c r="AR137" s="23" t="n"/>
+      <c r="AS137" s="23" t="n"/>
+      <c r="AT137" s="23" t="n"/>
     </row>
     <row r="138" ht="15" customHeight="1">
       <c r="A138" s="7" t="n"/>
       <c r="B138" s="7" t="n"/>
       <c r="C138" s="23" t="n"/>
-    </row>
-    <row r="139"/>
-    <row r="140"/>
+      <c r="D138" s="60" t="n"/>
+    </row>
+    <row r="139" ht="15" customHeight="1">
+      <c r="A139" s="7" t="n"/>
+      <c r="B139" s="7" t="n"/>
+      <c r="C139" s="23" t="n"/>
+    </row>
+    <row r="140" ht="15" customHeight="1">
+      <c r="A140" s="7" t="n"/>
+      <c r="B140" s="7" t="n"/>
+      <c r="C140" s="23" t="n"/>
+    </row>
+    <row r="141" ht="15" customHeight="1">
+      <c r="A141" s="7" t="n"/>
+      <c r="B141" s="7" t="n"/>
+      <c r="C141" s="23" t="n"/>
+      <c r="D141" s="23" t="n"/>
+      <c r="E141" s="23" t="n"/>
+      <c r="F141" s="23" t="n"/>
+      <c r="G141" s="23" t="n"/>
+      <c r="H141" s="23" t="n"/>
+      <c r="I141" s="23" t="n"/>
+      <c r="J141" s="23" t="n"/>
+      <c r="K141" s="23" t="n"/>
+      <c r="L141" s="23" t="n"/>
+      <c r="M141" s="23" t="n"/>
+      <c r="N141" s="23" t="n"/>
+      <c r="O141" s="23" t="n"/>
+      <c r="P141" s="23" t="n"/>
+      <c r="Q141" s="23" t="n"/>
+      <c r="R141" s="23" t="n"/>
+      <c r="S141" s="23" t="n"/>
+      <c r="T141" s="23" t="n"/>
+      <c r="U141" s="23" t="n"/>
+      <c r="V141" s="23" t="n"/>
+      <c r="W141" s="23" t="n"/>
+      <c r="X141" s="23" t="n"/>
+      <c r="Y141" s="23" t="n"/>
+      <c r="Z141" s="23" t="n"/>
+      <c r="AA141" s="23" t="n"/>
+      <c r="AB141" s="23" t="n"/>
+      <c r="AC141" s="23" t="n"/>
+      <c r="AD141" s="23" t="n"/>
+      <c r="AE141" s="23" t="n"/>
+      <c r="AF141" s="23" t="n"/>
+      <c r="AG141" s="23" t="n"/>
+      <c r="AH141" s="23" t="n"/>
+      <c r="AI141" s="23" t="n"/>
+      <c r="AJ141" s="23" t="n"/>
+      <c r="AK141" s="23" t="n"/>
+      <c r="AL141" s="23" t="n"/>
+      <c r="AM141" s="23" t="n"/>
+      <c r="AN141" s="23" t="n"/>
+      <c r="AO141" s="23" t="n"/>
+      <c r="AP141" s="23" t="n"/>
+      <c r="AQ141" s="23" t="n"/>
+      <c r="AR141" s="23" t="n"/>
+      <c r="AS141" s="23" t="n"/>
+      <c r="AT141" s="23" t="n"/>
+    </row>
+    <row r="142" ht="15" customHeight="1">
+      <c r="A142" s="7" t="n"/>
+      <c r="B142" s="7" t="n"/>
+      <c r="C142" s="23" t="n"/>
+      <c r="D142" s="25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G142" s="26" t="inlineStr">
+        <is>
+          <t>ANOTAÇÕES</t>
+        </is>
+      </c>
+      <c r="Y142" s="23" t="n"/>
+      <c r="Z142" s="23" t="n"/>
+      <c r="AA142" s="23" t="n"/>
+      <c r="AB142" s="23" t="n"/>
+      <c r="AC142" s="23" t="n"/>
+      <c r="AD142" s="23" t="n"/>
+      <c r="AE142" s="23" t="n"/>
+      <c r="AF142" s="23" t="n"/>
+      <c r="AG142" s="23" t="n"/>
+      <c r="AH142" s="23" t="n"/>
+      <c r="AI142" s="23" t="n"/>
+      <c r="AJ142" s="23" t="n"/>
+      <c r="AK142" s="23" t="n"/>
+      <c r="AL142" s="23" t="n"/>
+      <c r="AM142" s="23" t="n"/>
+      <c r="AN142" s="23" t="n"/>
+      <c r="AO142" s="23" t="n"/>
+      <c r="AP142" s="23" t="n"/>
+      <c r="AQ142" s="23" t="n"/>
+      <c r="AR142" s="23" t="n"/>
+      <c r="AS142" s="23" t="n"/>
+      <c r="AT142" s="23" t="n"/>
+    </row>
+    <row r="143" ht="15" customHeight="1">
+      <c r="A143" s="7" t="n"/>
+      <c r="B143" s="7" t="n"/>
+      <c r="C143" s="23" t="n"/>
+      <c r="G143" s="23" t="n"/>
+      <c r="H143" s="23" t="n"/>
+      <c r="I143" s="23" t="n"/>
+      <c r="J143" s="23" t="n"/>
+      <c r="K143" s="23" t="n"/>
+      <c r="L143" s="23" t="n"/>
+      <c r="M143" s="23" t="n"/>
+      <c r="N143" s="23" t="n"/>
+      <c r="O143" s="23" t="n"/>
+      <c r="P143" s="23" t="n"/>
+      <c r="Q143" s="23" t="n"/>
+      <c r="R143" s="23" t="n"/>
+      <c r="S143" s="23" t="n"/>
+      <c r="T143" s="23" t="n"/>
+      <c r="U143" s="23" t="n"/>
+      <c r="V143" s="23" t="n"/>
+      <c r="W143" s="23" t="n"/>
+      <c r="X143" s="23" t="n"/>
+      <c r="Y143" s="23" t="n"/>
+      <c r="Z143" s="23" t="n"/>
+      <c r="AA143" s="23" t="n"/>
+      <c r="AB143" s="23" t="n"/>
+      <c r="AC143" s="23" t="n"/>
+      <c r="AD143" s="23" t="n"/>
+      <c r="AE143" s="23" t="n"/>
+      <c r="AF143" s="23" t="n"/>
+      <c r="AG143" s="23" t="n"/>
+      <c r="AH143" s="23" t="n"/>
+      <c r="AI143" s="23" t="n"/>
+      <c r="AJ143" s="23" t="n"/>
+      <c r="AK143" s="23" t="n"/>
+      <c r="AL143" s="23" t="n"/>
+      <c r="AM143" s="23" t="n"/>
+      <c r="AN143" s="23" t="n"/>
+      <c r="AO143" s="23" t="n"/>
+      <c r="AP143" s="23" t="n"/>
+      <c r="AQ143" s="23" t="n"/>
+      <c r="AR143" s="23" t="n"/>
+      <c r="AS143" s="23" t="n"/>
+      <c r="AT143" s="23" t="n"/>
+    </row>
+    <row r="144" ht="15" customHeight="1">
+      <c r="A144" s="7" t="n"/>
+      <c r="B144" s="7" t="n"/>
+      <c r="C144" s="23" t="n"/>
+      <c r="D144" s="35" t="n"/>
+    </row>
+    <row r="145" ht="15" customHeight="1">
+      <c r="A145" s="7" t="n"/>
+      <c r="B145" s="7" t="n"/>
+      <c r="C145" s="23" t="n"/>
+    </row>
+    <row r="146" ht="15" customHeight="1">
+      <c r="A146" s="7" t="n"/>
+      <c r="B146" s="7" t="n"/>
+      <c r="C146" s="23" t="n"/>
+    </row>
+    <row r="147"/>
+    <row r="148"/>
   </sheetData>
-  <mergeCells count="360">
+  <mergeCells count="376">
     <mergeCell ref="D116:F116"/>
     <mergeCell ref="D2:X2"/>
     <mergeCell ref="Q119:W119"/>
     <mergeCell ref="D39:M39"/>
+    <mergeCell ref="G129:P129"/>
     <mergeCell ref="AC62:AD62"/>
     <mergeCell ref="AH2:AT2"/>
-    <mergeCell ref="M79:N79"/>
     <mergeCell ref="AB116:AT116"/>
     <mergeCell ref="M70:N70"/>
     <mergeCell ref="AB103:AT103"/>
     <mergeCell ref="M60:N60"/>
     <mergeCell ref="T67:Z67"/>
+    <mergeCell ref="G131:P131"/>
+    <mergeCell ref="G136:AL136"/>
     <mergeCell ref="AB118:AT118"/>
     <mergeCell ref="O63:P63"/>
     <mergeCell ref="Q116:W116"/>
     <mergeCell ref="AB117:AT117"/>
     <mergeCell ref="A8:B26"/>
+    <mergeCell ref="D129:F129"/>
     <mergeCell ref="AF22:AK22"/>
-    <mergeCell ref="D134:F135"/>
     <mergeCell ref="D119:F119"/>
     <mergeCell ref="Q122:W122"/>
     <mergeCell ref="F66:L66"/>
@@ -8907,18 +9239,20 @@
     <mergeCell ref="G119:P119"/>
     <mergeCell ref="E88:L88"/>
     <mergeCell ref="Q104:W104"/>
+    <mergeCell ref="D130:F130"/>
     <mergeCell ref="Q106:W106"/>
     <mergeCell ref="D117:F117"/>
     <mergeCell ref="AB124:AT124"/>
     <mergeCell ref="AC64:AD64"/>
     <mergeCell ref="R88:X88"/>
+    <mergeCell ref="D132:F132"/>
     <mergeCell ref="M86:Q86"/>
     <mergeCell ref="J23:N24"/>
+    <mergeCell ref="T76:X76"/>
     <mergeCell ref="O71:P71"/>
     <mergeCell ref="AB16:AH16"/>
     <mergeCell ref="AC65:AD65"/>
     <mergeCell ref="AB119:AT119"/>
-    <mergeCell ref="M76:N76"/>
     <mergeCell ref="O76:P76"/>
     <mergeCell ref="Q109:W109"/>
     <mergeCell ref="L17:R18"/>
@@ -8926,10 +9260,12 @@
     <mergeCell ref="T60:Z60"/>
     <mergeCell ref="O77:P77"/>
     <mergeCell ref="AK44:AT44"/>
+    <mergeCell ref="Q130:AT130"/>
     <mergeCell ref="X114:AA114"/>
     <mergeCell ref="AF30:AK30"/>
+    <mergeCell ref="Q132:AT132"/>
     <mergeCell ref="D122:F122"/>
-    <mergeCell ref="D130:AT132"/>
+    <mergeCell ref="G142:X142"/>
     <mergeCell ref="F69:L69"/>
     <mergeCell ref="AF31:AK31"/>
     <mergeCell ref="O53:X53"/>
@@ -8938,12 +9274,13 @@
     <mergeCell ref="D27:H28"/>
     <mergeCell ref="D30:N30"/>
     <mergeCell ref="E85:L85"/>
-    <mergeCell ref="T79:Z79"/>
     <mergeCell ref="D16:J16"/>
+    <mergeCell ref="T77:X77"/>
     <mergeCell ref="F67:L67"/>
     <mergeCell ref="G113:P113"/>
     <mergeCell ref="AB19:AH19"/>
     <mergeCell ref="AJ16:AP16"/>
+    <mergeCell ref="F80:J80"/>
     <mergeCell ref="AB17:AH18"/>
     <mergeCell ref="Q112:W112"/>
     <mergeCell ref="T17:Z18"/>
@@ -8951,31 +9288,37 @@
     <mergeCell ref="X101:AA101"/>
     <mergeCell ref="AA69:AB69"/>
     <mergeCell ref="E86:L86"/>
+    <mergeCell ref="D138:AT140"/>
     <mergeCell ref="AM27:AR27"/>
     <mergeCell ref="N11:V11"/>
     <mergeCell ref="AA64:AB64"/>
     <mergeCell ref="O67:P67"/>
+    <mergeCell ref="Y78:AB78"/>
     <mergeCell ref="AC80:AD80"/>
     <mergeCell ref="AM22:AR22"/>
     <mergeCell ref="X104:AA104"/>
+    <mergeCell ref="Y80:AB80"/>
     <mergeCell ref="T70:Z70"/>
     <mergeCell ref="X106:AA106"/>
     <mergeCell ref="W94:AT94"/>
     <mergeCell ref="D94:M94"/>
     <mergeCell ref="X110:AA110"/>
     <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="F76:J76"/>
     <mergeCell ref="AH10:AL10"/>
     <mergeCell ref="D19:J19"/>
     <mergeCell ref="L16:R16"/>
     <mergeCell ref="AC79:AD79"/>
     <mergeCell ref="G115:P115"/>
     <mergeCell ref="O39:X39"/>
+    <mergeCell ref="K76:N76"/>
     <mergeCell ref="D10:L10"/>
     <mergeCell ref="D93:T93"/>
     <mergeCell ref="D26:N26"/>
     <mergeCell ref="T66:Z66"/>
     <mergeCell ref="AK40:AT40"/>
     <mergeCell ref="Z44:AI44"/>
+    <mergeCell ref="D134:AT134"/>
     <mergeCell ref="D106:F106"/>
     <mergeCell ref="D54:M54"/>
     <mergeCell ref="X105:AA105"/>
@@ -8985,6 +9328,7 @@
     <mergeCell ref="X107:AA107"/>
     <mergeCell ref="D95:M95"/>
     <mergeCell ref="D109:F109"/>
+    <mergeCell ref="F77:J77"/>
     <mergeCell ref="Z47:AI47"/>
     <mergeCell ref="D97:M97"/>
     <mergeCell ref="D111:F111"/>
@@ -8995,31 +9339,28 @@
     <mergeCell ref="D104:F104"/>
     <mergeCell ref="AB111:AT111"/>
     <mergeCell ref="M68:N68"/>
-    <mergeCell ref="D126:AT126"/>
     <mergeCell ref="AJ17:AP18"/>
     <mergeCell ref="G37:X37"/>
     <mergeCell ref="M67:N67"/>
+    <mergeCell ref="Y76:AB76"/>
     <mergeCell ref="G109:P109"/>
     <mergeCell ref="M69:N69"/>
     <mergeCell ref="N10:V10"/>
     <mergeCell ref="G111:P111"/>
     <mergeCell ref="D44:M44"/>
-    <mergeCell ref="AA78:AB78"/>
     <mergeCell ref="AA65:AB65"/>
-    <mergeCell ref="M81:N81"/>
-    <mergeCell ref="G134:X134"/>
     <mergeCell ref="P31:AD32"/>
     <mergeCell ref="AK43:AT43"/>
-    <mergeCell ref="AA80:AB80"/>
     <mergeCell ref="Z53:AI53"/>
+    <mergeCell ref="Q128:AT128"/>
     <mergeCell ref="AB109:AT109"/>
     <mergeCell ref="X121:AA121"/>
     <mergeCell ref="AA62:AB62"/>
-    <mergeCell ref="F81:L81"/>
     <mergeCell ref="D101:F101"/>
     <mergeCell ref="X123:AA123"/>
     <mergeCell ref="O40:X40"/>
     <mergeCell ref="G114:P114"/>
+    <mergeCell ref="D142:F143"/>
     <mergeCell ref="AB101:AT101"/>
     <mergeCell ref="T16:Z16"/>
     <mergeCell ref="D98:M98"/>
@@ -9028,28 +9369,26 @@
     <mergeCell ref="AN10:AT10"/>
     <mergeCell ref="Z40:AI40"/>
     <mergeCell ref="AM30:AR30"/>
+    <mergeCell ref="G130:P130"/>
     <mergeCell ref="D114:F114"/>
     <mergeCell ref="O69:P69"/>
     <mergeCell ref="G117:P117"/>
     <mergeCell ref="Z54:AI54"/>
-    <mergeCell ref="M77:N77"/>
+    <mergeCell ref="G132:P132"/>
     <mergeCell ref="AB114:AT114"/>
-    <mergeCell ref="T78:Z78"/>
     <mergeCell ref="AK39:AT39"/>
     <mergeCell ref="Z43:AI43"/>
     <mergeCell ref="O64:P64"/>
     <mergeCell ref="G112:P112"/>
-    <mergeCell ref="T80:Z80"/>
     <mergeCell ref="N94:V94"/>
     <mergeCell ref="D53:M53"/>
     <mergeCell ref="D47:M47"/>
-    <mergeCell ref="AA79:AB79"/>
     <mergeCell ref="AC70:AD70"/>
     <mergeCell ref="G8:X8"/>
-    <mergeCell ref="D136:AT140"/>
     <mergeCell ref="O47:X47"/>
     <mergeCell ref="Q123:W123"/>
     <mergeCell ref="Q110:W110"/>
+    <mergeCell ref="Q131:AT131"/>
     <mergeCell ref="AB112:AT112"/>
     <mergeCell ref="D102:F102"/>
     <mergeCell ref="AC76:AD76"/>
@@ -9059,6 +9398,7 @@
     <mergeCell ref="T68:Z68"/>
     <mergeCell ref="AC60:AD60"/>
     <mergeCell ref="O60:P60"/>
+    <mergeCell ref="D128:F128"/>
     <mergeCell ref="AM23:AR23"/>
     <mergeCell ref="AB122:AT122"/>
     <mergeCell ref="R86:X86"/>
@@ -9070,6 +9410,7 @@
     <mergeCell ref="Q105:W105"/>
     <mergeCell ref="O48:X48"/>
     <mergeCell ref="Q120:W120"/>
+    <mergeCell ref="D126:AD126"/>
     <mergeCell ref="Q107:W107"/>
     <mergeCell ref="AC78:AD78"/>
     <mergeCell ref="F64:L64"/>
@@ -9086,17 +9427,18 @@
     <mergeCell ref="N96:V96"/>
     <mergeCell ref="D37:F38"/>
     <mergeCell ref="D5:Z5"/>
-    <mergeCell ref="T76:Z76"/>
     <mergeCell ref="G110:P110"/>
     <mergeCell ref="T69:Z69"/>
     <mergeCell ref="N98:V98"/>
     <mergeCell ref="AC66:AD66"/>
+    <mergeCell ref="T78:X78"/>
     <mergeCell ref="AC68:AD68"/>
     <mergeCell ref="E87:L87"/>
     <mergeCell ref="AC67:AD67"/>
     <mergeCell ref="AB121:AT121"/>
-    <mergeCell ref="F78:L78"/>
+    <mergeCell ref="T80:X80"/>
     <mergeCell ref="G51:X51"/>
+    <mergeCell ref="T79:X79"/>
     <mergeCell ref="D23:H24"/>
     <mergeCell ref="AC69:AD69"/>
     <mergeCell ref="AB123:AT123"/>
@@ -9107,6 +9449,7 @@
     <mergeCell ref="M85:Q85"/>
     <mergeCell ref="O79:P79"/>
     <mergeCell ref="O70:P70"/>
+    <mergeCell ref="Y79:AB79"/>
     <mergeCell ref="O81:P81"/>
     <mergeCell ref="A30:B48"/>
     <mergeCell ref="D124:F124"/>
@@ -9120,7 +9463,6 @@
     <mergeCell ref="X115:AA115"/>
     <mergeCell ref="W97:AT97"/>
     <mergeCell ref="X102:AA102"/>
-    <mergeCell ref="T77:Z77"/>
     <mergeCell ref="W96:AT96"/>
     <mergeCell ref="G14:X14"/>
     <mergeCell ref="AH3:AT3"/>
@@ -9133,9 +9475,7 @@
     <mergeCell ref="AH11:AL11"/>
     <mergeCell ref="M61:N61"/>
     <mergeCell ref="D91:F92"/>
-    <mergeCell ref="F80:L80"/>
     <mergeCell ref="P23:AD24"/>
-    <mergeCell ref="F79:L79"/>
     <mergeCell ref="G104:P104"/>
     <mergeCell ref="T61:Z61"/>
     <mergeCell ref="O78:P78"/>
@@ -9155,40 +9495,46 @@
     <mergeCell ref="X103:AA103"/>
     <mergeCell ref="G101:P101"/>
     <mergeCell ref="AB106:AT106"/>
-    <mergeCell ref="F76:L76"/>
     <mergeCell ref="X118:AA118"/>
     <mergeCell ref="M62:N62"/>
     <mergeCell ref="AK54:AT54"/>
     <mergeCell ref="O66:P66"/>
     <mergeCell ref="D105:F105"/>
+    <mergeCell ref="F78:J78"/>
     <mergeCell ref="D120:F120"/>
     <mergeCell ref="X122:AA122"/>
     <mergeCell ref="O68:P68"/>
     <mergeCell ref="D107:F107"/>
+    <mergeCell ref="Y77:AB77"/>
     <mergeCell ref="D51:F52"/>
     <mergeCell ref="M64:N64"/>
     <mergeCell ref="G106:P106"/>
+    <mergeCell ref="K78:N78"/>
     <mergeCell ref="J31:N32"/>
     <mergeCell ref="G105:P105"/>
     <mergeCell ref="X111:AA111"/>
+    <mergeCell ref="K80:N80"/>
     <mergeCell ref="AA70:AB70"/>
     <mergeCell ref="M65:N65"/>
     <mergeCell ref="G120:P120"/>
     <mergeCell ref="G107:P107"/>
     <mergeCell ref="D40:M40"/>
+    <mergeCell ref="K79:N79"/>
+    <mergeCell ref="K81:N81"/>
     <mergeCell ref="Q103:W103"/>
-    <mergeCell ref="AA76:AB76"/>
+    <mergeCell ref="D144:AT148"/>
     <mergeCell ref="D108:F108"/>
     <mergeCell ref="X117:AA117"/>
     <mergeCell ref="AB120:AT120"/>
-    <mergeCell ref="F77:L77"/>
     <mergeCell ref="X109:AA109"/>
     <mergeCell ref="G57:AD57"/>
     <mergeCell ref="T19:Z19"/>
     <mergeCell ref="G102:P102"/>
-    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="F79:J79"/>
     <mergeCell ref="D121:F121"/>
     <mergeCell ref="D113:F113"/>
+    <mergeCell ref="Q129:AT129"/>
+    <mergeCell ref="F81:J81"/>
     <mergeCell ref="D123:F123"/>
     <mergeCell ref="D57:F58"/>
     <mergeCell ref="AB113:AT113"/>
@@ -9196,11 +9542,11 @@
     <mergeCell ref="Q118:W118"/>
     <mergeCell ref="N95:V95"/>
     <mergeCell ref="O54:X54"/>
+    <mergeCell ref="G128:P128"/>
     <mergeCell ref="X112:AA112"/>
     <mergeCell ref="AB115:AT115"/>
     <mergeCell ref="D48:M48"/>
     <mergeCell ref="Q113:W113"/>
-    <mergeCell ref="G128:AH128"/>
     <mergeCell ref="AB102:AT102"/>
     <mergeCell ref="N97:V97"/>
     <mergeCell ref="G121:P121"/>
@@ -9213,12 +9559,10 @@
     <mergeCell ref="D17:J18"/>
     <mergeCell ref="D103:F103"/>
     <mergeCell ref="M88:Q88"/>
-    <mergeCell ref="AA77:AB77"/>
     <mergeCell ref="AC77:AD77"/>
-    <mergeCell ref="D128:F129"/>
     <mergeCell ref="D118:F118"/>
     <mergeCell ref="AK53:AT53"/>
-    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="D136:F137"/>
     <mergeCell ref="AA66:AB66"/>
     <mergeCell ref="O80:P80"/>
     <mergeCell ref="G116:P116"/>
@@ -9229,13 +9573,15 @@
     <mergeCell ref="O44:X44"/>
     <mergeCell ref="F70:L70"/>
     <mergeCell ref="G118:P118"/>
+    <mergeCell ref="D131:F131"/>
+    <mergeCell ref="K77:N77"/>
     <mergeCell ref="T64:Z64"/>
     <mergeCell ref="AA67:AB67"/>
     <mergeCell ref="AA61:AB61"/>
     <mergeCell ref="AC61:AD61"/>
     <mergeCell ref="D83:F84"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="14">
     <dataValidation sqref="D11:L11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$A$4:$A$7</formula1>
     </dataValidation>
@@ -9244,6 +9590,39 @@
     </dataValidation>
     <dataValidation sqref="X11:AF11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$I$4:$I$10</formula1>
+    </dataValidation>
+    <dataValidation sqref="K76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$K$4:$K$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="K77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$K$4:$K$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="K78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$K$4:$K$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="K79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$K$4:$K$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="K80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$K$4:$K$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="K81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$K$4:$K$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$K$4:$K$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$K$4:$K$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$K$4:$K$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$K$4:$K$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="Y80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$K$4:$K$8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15066,7 +15445,7 @@
       </c>
       <c r="K4" s="82" t="inlineStr">
         <is>
-          <t>lista</t>
+          <t>Força</t>
         </is>
       </c>
       <c r="L4" s="82" t="inlineStr">
@@ -15212,7 +15591,7 @@
       </c>
       <c r="K5" s="82" t="inlineStr">
         <is>
-          <t>escala</t>
+          <t>Destreza</t>
         </is>
       </c>
       <c r="L5" s="82" t="inlineStr">
@@ -15344,7 +15723,7 @@
       </c>
       <c r="K6" s="82" t="inlineStr">
         <is>
-          <t>criacao</t>
+          <t>Constituição</t>
         </is>
       </c>
       <c r="L6" s="82" t="inlineStr">
@@ -15476,7 +15855,7 @@
       </c>
       <c r="K7" s="82" t="inlineStr">
         <is>
-          <t>nota</t>
+          <t>Inteligência</t>
         </is>
       </c>
       <c r="L7" s="82" t="inlineStr">
@@ -15600,7 +15979,7 @@
       <c r="J8" s="23" t="n"/>
       <c r="K8" s="82" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>Essência</t>
         </is>
       </c>
       <c r="L8" s="82" t="inlineStr">

--- a/ficha/ficha-projeto-m.xlsx
+++ b/ficha/ficha-projeto-m.xlsx
@@ -625,6 +625,40 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Projeto M</author>
+  </authors>
+  <commentList>
+    <comment ref="AF23" authorId="0" shapeId="0">
+      <text>
+        <t>Vida temporária é anteparo, e não vida.
+• É gasta antes da vida normal.
+• Não empilha: duas fontes, fica a maior.
+• Teto: metade da sua vida máxima.
+• Some no fim da cena.
+Livro, cap. 10. A Melhoria Rasga Escudo ignora ela.</t>
+      </text>
+    </comment>
+    <comment ref="AF27" authorId="0" shapeId="0">
+      <text>
+        <t>Energia temporária gasta como PE, e gasta primeiro.
+• Acumula até o teto que a própria fonte declarar.
+• Hoje só o Braseiro concede, e o teto dele é 2.
+• Some no fim da cena.</t>
+      </text>
+    </comment>
+    <comment ref="AF31" authorId="0" shapeId="0">
+      <text>
+        <t>⚠ Regra nenhuma concede integridade temporária hoje.
+O campo existe porque as três reservas são montadas no mesmo laço. Está em aberto (B17) e é decisão de desenho: ou algo passa a conceder, ou o campo sai.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -9628,6 +9662,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/ficha/ficha-projeto-m.xlsx
+++ b/ficha/ficha-projeto-m.xlsx
@@ -652,7 +652,8 @@
     <comment ref="AF31" authorId="0" shapeId="0">
       <text>
         <t>⚠ Regra nenhuma concede integridade temporária hoje.
-O campo existe porque as três reservas são montadas no mesmo laço. Está em aberto (B17) e é decisão de desenho: ou algo passa a conceder, ou o campo sai.</t>
+O campo fica assim mesmo — é espaço do mestre: se alguma coisa na mesa conceder, anote aqui.
+A ficha já trata ele como as outras duas: um delta negativo come a temporária antes da Integridade, e ela nunca fica negativa.</t>
       </text>
     </comment>
   </commentList>

--- a/ficha/ficha-projeto-m.xlsx
+++ b/ficha/ficha-projeto-m.xlsx
@@ -641,6 +641,12 @@
 Livro, cap. 10. A Melhoria Rasga Escudo ignora ela.</t>
       </text>
     </comment>
+    <comment ref="AM23" authorId="0" shapeId="0">
+      <text>
+        <t>Valor negativo para perda, positivo para ganho. Espere alguns segundos.
+A perda come a vida temporária antes da vida.</t>
+      </text>
+    </comment>
     <comment ref="AF27" authorId="0" shapeId="0">
       <text>
         <t>Energia temporária gasta como PE, e gasta primeiro.
@@ -649,11 +655,24 @@
 • Some no fim da cena.</t>
       </text>
     </comment>
+    <comment ref="AM27" authorId="0" shapeId="0">
+      <text>
+        <t>Valor negativo para gasto, positivo para ganho. Espere alguns segundos.
+O gasto come a energia temporária primeiro.</t>
+      </text>
+    </comment>
     <comment ref="AF31" authorId="0" shapeId="0">
       <text>
         <t>⚠ Regra nenhuma concede integridade temporária hoje.
 O campo fica assim mesmo — é espaço do mestre: se alguma coisa na mesa conceder, anote aqui.
 A ficha já trata ele como as outras duas: um delta negativo come a temporária antes da Integridade, e ela nunca fica negativa.</t>
+      </text>
+    </comment>
+    <comment ref="AM31" authorId="0" shapeId="0">
+      <text>
+        <t>Valor negativo para perda, positivo para ganho. Espere alguns segundos.
+⚠ A PERDA AQUI TIRA VIDA JUNTO, no mesmo tanto: cada ponto de dano na alma tira 1 de vida e 1 de Integridade (livro, cap. 15).
+Exceção: o Cisão atravessa o corpo e tira só Integridade. Para ele, edite a Integridade na mão em vez de usar esta caixinha.</t>
       </text>
     </comment>
   </commentList>
